--- a/out/global_metric/excel/vit.xlsx
+++ b/out/global_metric/excel/vit.xlsx
@@ -496,25 +496,29 @@
         <v>21</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9702380895614624</v>
+        <v>0.7572156190872192</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9681516536466476</v>
+        <v>0.7572044169343199</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>221</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="G2" t="n">
-        <v>103</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>225</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8259425804219993</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.8151721948323422</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>vit</t>
@@ -534,25 +538,29 @@
         <v>44</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9345238208770752</v>
+        <v>0.7809846997261047</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9303771187951062</v>
+        <v>0.7803363378871853</v>
       </c>
       <c r="D3" t="n">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="E3" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="G3" t="n">
-        <v>99</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>246</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8582958607171682</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8469341050189541</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>vit</t>
@@ -572,25 +580,29 @@
         <v>67</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9464285969734192</v>
+        <v>0.7758913636207581</v>
       </c>
       <c r="C4" t="n">
-        <v>0.943035823536655</v>
+        <v>0.7757044885046017</v>
       </c>
       <c r="D4" t="n">
-        <v>59</v>
+        <v>220</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="G4" t="n">
-        <v>100</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>237</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8649832814481725</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8723301405638898</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>vit</t>
@@ -610,25 +622,29 @@
         <v>90</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9404761791229248</v>
+        <v>0.7826825380325317</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9368990333437516</v>
+        <v>0.7809085364183828</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>204</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="G5" t="n">
-        <v>99</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8650755217341174</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.8394087113647201</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>vit</t>
@@ -648,25 +664,29 @@
         <v>113</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9642857313156128</v>
+        <v>0.7792869210243225</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9623599650072854</v>
+        <v>0.7792862857610978</v>
       </c>
       <c r="D6" t="n">
-        <v>62</v>
+        <v>229</v>
       </c>
       <c r="E6" t="n">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
-        <v>100</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>230</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8515680848610631</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8409543456681697</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>vit</t>
@@ -762,25 +782,29 @@
         <v>22</v>
       </c>
       <c r="B2" t="n">
-        <v>0.9523809552192688</v>
+        <v>0.7249575257301331</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9488740058382286</v>
+        <v>0.7249567573414044</v>
       </c>
       <c r="D2" t="n">
-        <v>58</v>
+        <v>214</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="G2" t="n">
-        <v>102</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>213</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8065605903378301</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.7672439716560772</v>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>vit</t>
@@ -800,25 +824,29 @@
         <v>45</v>
       </c>
       <c r="B3" t="n">
-        <v>0.9404761791229248</v>
+        <v>0.7640067934989929</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9365079313903756</v>
+        <v>0.7637343718280007</v>
       </c>
       <c r="D3" t="n">
-        <v>58</v>
+        <v>215</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>235</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8382278335062838</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.8232195215578459</v>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>vit</t>
@@ -838,25 +866,29 @@
         <v>68</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9523809552192688</v>
+        <v>0.7572156190872192</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9498132883845936</v>
+        <v>0.7572156146686998</v>
       </c>
       <c r="D4" t="n">
-        <v>61</v>
+        <v>223</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
-        <v>99</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>223</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8487489911218724</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8388978585680458</v>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>vit</t>
@@ -876,25 +908,29 @@
         <v>91</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9404761791229248</v>
+        <v>0.7674023509025574</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9360925085788666</v>
+        <v>0.7671849388754889</v>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>217</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>77</v>
       </c>
       <c r="G5" t="n">
-        <v>101</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>235</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8262884814942928</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.7856352729687432</v>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>vit</t>
@@ -914,25 +950,29 @@
         <v>114</v>
       </c>
       <c r="B6" t="n">
-        <v>0.9464285969734192</v>
+        <v>0.7623090147972107</v>
       </c>
       <c r="C6" t="n">
-        <v>0.942672980664324</v>
+        <v>0.7622534836153311</v>
       </c>
       <c r="D6" t="n">
-        <v>58</v>
+        <v>229</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="G6" t="n">
-        <v>101</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8512740689496137</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.8493237268611182</v>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>vit</t>

--- a/out/global_metric/excel/vit.xlsx
+++ b/out/global_metric/excel/vit.xlsx
@@ -496,28 +496,28 @@
         <v>21</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7572156190872192</v>
+        <v>0.7640067934989929</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7572044169343199</v>
+        <v>0.764004065112001</v>
       </c>
       <c r="D2" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G2" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8259425804219993</v>
+        <v>0.838498789346247</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8151721948323422</v>
+        <v>0.8242494385674135</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -538,28 +538,28 @@
         <v>44</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7809846997261047</v>
+        <v>0.7826825380325317</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7803363378871853</v>
+        <v>0.7824561353289725</v>
       </c>
       <c r="D3" t="n">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E3" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="G3" t="n">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8582958607171682</v>
+        <v>0.8748472270264037</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8469341050189541</v>
+        <v>0.868463314908691</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -580,28 +580,28 @@
         <v>67</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7758913636207581</v>
+        <v>0.804753839969635</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7757044885046017</v>
+        <v>0.8046434443946746</v>
       </c>
       <c r="D4" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="E4" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F4" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G4" t="n">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8649832814481725</v>
+        <v>0.8712210307851955</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8723301405638898</v>
+        <v>0.8594257612775626</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -622,28 +622,28 @@
         <v>90</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7826825380325317</v>
+        <v>0.7860780954360962</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7809085364183828</v>
+        <v>0.7860034551823591</v>
       </c>
       <c r="D5" t="n">
-        <v>204</v>
+        <v>237</v>
       </c>
       <c r="E5" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="F5" t="n">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="G5" t="n">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8650755217341174</v>
+        <v>0.8628156347284677</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8394087113647201</v>
+        <v>0.8600602500138065</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -664,28 +664,28 @@
         <v>113</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7792869210243225</v>
+        <v>0.7741935253143311</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7792862857610978</v>
+        <v>0.7741701089891481</v>
       </c>
       <c r="D6" t="n">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="E6" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8515680848610631</v>
+        <v>0.8724778046811945</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8409543456681697</v>
+        <v>0.883316111821922</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -782,28 +782,28 @@
         <v>22</v>
       </c>
       <c r="B2" t="n">
-        <v>0.7249575257301331</v>
+        <v>0.7674023509025574</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7249567573414044</v>
+        <v>0.7672306066628178</v>
       </c>
       <c r="D2" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E2" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8065605903378301</v>
+        <v>0.8274645451400899</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7672439716560772</v>
+        <v>0.7782350689171464</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -824,28 +824,28 @@
         <v>45</v>
       </c>
       <c r="B3" t="n">
-        <v>0.7640067934989929</v>
+        <v>0.7809846997261047</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7637343718280007</v>
+        <v>0.7809746133852216</v>
       </c>
       <c r="D3" t="n">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="E3" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F3" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="G3" t="n">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8382278335062838</v>
+        <v>0.850714862216073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8232195215578459</v>
+        <v>0.8465471959295532</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -866,28 +866,28 @@
         <v>68</v>
       </c>
       <c r="B4" t="n">
-        <v>0.7572156190872192</v>
+        <v>0.8217317461967468</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7572156146686998</v>
+        <v>0.8217235215861408</v>
       </c>
       <c r="D4" t="n">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="F4" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="G4" t="n">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8487489911218724</v>
+        <v>0.8833390983512049</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8388978585680458</v>
+        <v>0.8796705568174787</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -908,28 +908,28 @@
         <v>91</v>
       </c>
       <c r="B5" t="n">
-        <v>0.7674023509025574</v>
+        <v>0.7724957466125488</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7671849388754889</v>
+        <v>0.7724636126780509</v>
       </c>
       <c r="D5" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="G5" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8262884814942928</v>
+        <v>0.8291709904300704</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7856352729687432</v>
+        <v>0.8021937678044778</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -950,28 +950,28 @@
         <v>114</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7623090147972107</v>
+        <v>0.7826825380325317</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7622534836153311</v>
+        <v>0.782541472236729</v>
       </c>
       <c r="D6" t="n">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G6" t="n">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8512740689496137</v>
+        <v>0.8668626772742996</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8493237268611182</v>
+        <v>0.8634848271746643</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
